--- a/api/대상티커2.xlsx
+++ b/api/대상티커2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\frontend\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDDC61C7-44B5-4C6D-A00B-8AF385726577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0DC410-6A3D-48AB-9AA4-F440AC41F385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8805" yWindow="1800" windowWidth="23865" windowHeight="14055" xr2:uid="{42E3D2C6-1E3A-49A4-82D0-16C14578AABA}"/>
+    <workbookView xWindow="4440" yWindow="1740" windowWidth="23865" windowHeight="14055" xr2:uid="{42E3D2C6-1E3A-49A4-82D0-16C14578AABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
   <si>
     <t>더코디</t>
   </si>
@@ -36,90 +36,48 @@
     <t>아이티센피엔에스</t>
   </si>
   <si>
-    <t>크리스탈신소재</t>
-  </si>
-  <si>
     <t>NPX</t>
   </si>
   <si>
-    <t>원풍물산</t>
-  </si>
-  <si>
-    <t>코스나인</t>
-  </si>
-  <si>
-    <t>THE E&amp;M</t>
-  </si>
-  <si>
     <t>인포뱅크</t>
   </si>
   <si>
     <t>이엠코리아</t>
   </si>
   <si>
-    <t>랩지노믹스</t>
-  </si>
-  <si>
-    <t>티엔엔터테인먼트</t>
-  </si>
-  <si>
-    <t>썸에이지</t>
-  </si>
-  <si>
     <t>우리기술투자</t>
   </si>
   <si>
     <t>선바이오</t>
   </si>
   <si>
-    <t>케이바이오</t>
-  </si>
-  <si>
-    <t>큐로홀딩스</t>
-  </si>
-  <si>
     <t>아이티센글로벌</t>
   </si>
   <si>
     <t>인지컨트롤스</t>
   </si>
   <si>
-    <t>CG인바이츠</t>
-  </si>
-  <si>
     <t>제이티</t>
   </si>
   <si>
     <t>툴젠</t>
   </si>
   <si>
-    <t>피플바이오</t>
-  </si>
-  <si>
     <t>HLB생명과학</t>
   </si>
   <si>
     <t>듀켐바이오</t>
   </si>
   <si>
-    <t>THE CUBE&amp;</t>
-  </si>
-  <si>
     <t>린드먼아시아</t>
   </si>
   <si>
     <t>에코캡</t>
   </si>
   <si>
-    <t>일진디스플</t>
-  </si>
-  <si>
     <t>바이넥스</t>
   </si>
   <si>
-    <t>다산솔루에타</t>
-  </si>
-  <si>
     <t>갤럭시아머니트리</t>
   </si>
   <si>
@@ -129,21 +87,12 @@
     <t>동신건설</t>
   </si>
   <si>
-    <t>동일스틸럭스</t>
-  </si>
-  <si>
     <t>픽셀플러스</t>
   </si>
   <si>
     <t>캐리소프트</t>
   </si>
   <si>
-    <t>오성첨단소재</t>
-  </si>
-  <si>
-    <t>손오공</t>
-  </si>
-  <si>
     <t>휴니드</t>
   </si>
   <si>
@@ -156,15 +105,9 @@
     <t>미래나노텍</t>
   </si>
   <si>
-    <t>한탑</t>
-  </si>
-  <si>
     <t>티에스아이</t>
   </si>
   <si>
-    <t>드래곤플라이</t>
-  </si>
-  <si>
     <t>유투바이오</t>
   </si>
   <si>
@@ -174,15 +117,9 @@
     <t>동진쎄미켐</t>
   </si>
   <si>
-    <t>디에이테크놀로지</t>
-  </si>
-  <si>
     <t>인카금융서비스</t>
   </si>
   <si>
-    <t>멕아이씨에스</t>
-  </si>
-  <si>
     <t>오스테오닉</t>
   </si>
   <si>
@@ -204,36 +141,15 @@
     <t>모트렉스</t>
   </si>
   <si>
-    <t>플레이그램</t>
-  </si>
-  <si>
     <t>이엔플러스</t>
   </si>
   <si>
-    <t>지엘팜텍</t>
-  </si>
-  <si>
-    <t>엔투텍</t>
-  </si>
-  <si>
     <t>에프에스티</t>
   </si>
   <si>
-    <t>에쓰씨엔지니어링</t>
-  </si>
-  <si>
     <t>제룡산업</t>
   </si>
   <si>
-    <t>한창</t>
-  </si>
-  <si>
-    <t>기가레인</t>
-  </si>
-  <si>
-    <t>캐리</t>
-  </si>
-  <si>
     <t>퍼스텍</t>
   </si>
   <si>
@@ -249,15 +165,6 @@
     <t>차바이오텍</t>
   </si>
   <si>
-    <t>바이온</t>
-  </si>
-  <si>
-    <t>이월드</t>
-  </si>
-  <si>
-    <t>케일럼</t>
-  </si>
-  <si>
     <t>제이엔케이글로벌</t>
   </si>
   <si>
@@ -273,9 +180,6 @@
     <t>빅텍</t>
   </si>
   <si>
-    <t>플루토스</t>
-  </si>
-  <si>
     <t>KBI메탈</t>
   </si>
   <si>
@@ -291,27 +195,18 @@
     <t>선샤인푸드</t>
   </si>
   <si>
-    <t>앱튼</t>
-  </si>
-  <si>
     <t>마이크로디지탈</t>
   </si>
   <si>
     <t>홈캐스트</t>
   </si>
   <si>
-    <t>투비소프트</t>
-  </si>
-  <si>
     <t>삼천당제약</t>
   </si>
   <si>
     <t>에이텍모빌리티</t>
   </si>
   <si>
-    <t>제이케이시냅스</t>
-  </si>
-  <si>
     <t>동국알앤에스</t>
   </si>
   <si>
@@ -324,9 +219,6 @@
     <t>케이엔더블유</t>
   </si>
   <si>
-    <t>주연테크</t>
-  </si>
-  <si>
     <t>칩스앤미디어</t>
   </si>
   <si>
@@ -357,9 +249,6 @@
     <t>리가켐바이오</t>
   </si>
   <si>
-    <t>아이진</t>
-  </si>
-  <si>
     <t>오르비텍</t>
   </si>
   <si>
@@ -372,21 +261,12 @@
     <t>나이벡</t>
   </si>
   <si>
-    <t>팬스타엔터프라이즈</t>
-  </si>
-  <si>
-    <t>삼일</t>
-  </si>
-  <si>
     <t>티앤알바이오팹</t>
   </si>
   <si>
     <t>한올바이오파마</t>
   </si>
   <si>
-    <t>리튬포어스</t>
-  </si>
-  <si>
     <t>에스트래픽</t>
   </si>
   <si>
@@ -396,9 +276,6 @@
     <t>나무기술</t>
   </si>
   <si>
-    <t>테라사이언스</t>
-  </si>
-  <si>
     <t>이오테크닉스</t>
   </si>
   <si>
@@ -408,9 +285,6 @@
     <t>디알텍</t>
   </si>
   <si>
-    <t>엔시트론</t>
-  </si>
-  <si>
     <t>원익큐브</t>
   </si>
   <si>
@@ -426,27 +300,18 @@
     <t>현대바이오</t>
   </si>
   <si>
-    <t>휴마시스</t>
-  </si>
-  <si>
     <t>폴라리스AI파마</t>
   </si>
   <si>
     <t>중앙에너비스</t>
   </si>
   <si>
-    <t>한국비티비</t>
-  </si>
-  <si>
     <t>나인테크</t>
   </si>
   <si>
     <t>LS마린솔루션</t>
   </si>
   <si>
-    <t>이원컴포텍</t>
-  </si>
-  <si>
     <t>퓨쳐켐</t>
   </si>
   <si>
@@ -459,9 +324,6 @@
     <t>엠로</t>
   </si>
   <si>
-    <t>프로브잇</t>
-  </si>
-  <si>
     <t>엠플러스</t>
   </si>
   <si>
@@ -474,9 +336,6 @@
     <t>흥구석유</t>
   </si>
   <si>
-    <t>캔버스엔</t>
-  </si>
-  <si>
     <t>앱클론</t>
   </si>
   <si>
@@ -486,9 +345,6 @@
     <t>플리토</t>
   </si>
   <si>
-    <t>까뮤이앤씨</t>
-  </si>
-  <si>
     <t>와이씨</t>
   </si>
   <si>
@@ -540,9 +396,6 @@
     <t>제룡전기</t>
   </si>
   <si>
-    <t>파라텍</t>
-  </si>
-  <si>
     <t>세기상사</t>
   </si>
   <si>
@@ -555,9 +408,6 @@
     <t>디아이티</t>
   </si>
   <si>
-    <t>에스티오</t>
-  </si>
-  <si>
     <t>신라에스지</t>
   </si>
   <si>
@@ -585,9 +435,6 @@
     <t>알파칩스</t>
   </si>
   <si>
-    <t>케스피온</t>
-  </si>
-  <si>
     <t>위메이드</t>
   </si>
   <si>
@@ -603,18 +450,12 @@
     <t>한창산업</t>
   </si>
   <si>
-    <t>소프트캠프</t>
-  </si>
-  <si>
     <t>동성화인텍</t>
   </si>
   <si>
     <t>스타플렉스</t>
   </si>
   <si>
-    <t>티사이언티픽</t>
-  </si>
-  <si>
     <t>씨이랩</t>
   </si>
   <si>
@@ -624,36 +465,21 @@
     <t>압타바이오</t>
   </si>
   <si>
-    <t>씨엔플러스</t>
-  </si>
-  <si>
     <t>대모</t>
   </si>
   <si>
     <t>아모그린텍</t>
   </si>
   <si>
-    <t>아센디오</t>
-  </si>
-  <si>
     <t>덕성우</t>
   </si>
   <si>
-    <t>셀피글로벌</t>
-  </si>
-  <si>
     <t>미디어젠</t>
   </si>
   <si>
     <t>두산2우B</t>
   </si>
   <si>
-    <t>우리로</t>
-  </si>
-  <si>
-    <t>HLB바이오스텝</t>
-  </si>
-  <si>
     <t>삼일제약</t>
   </si>
   <si>
@@ -684,15 +510,6 @@
     <t>동양2우B</t>
   </si>
   <si>
-    <t>네오리진</t>
-  </si>
-  <si>
-    <t>카이노스메드</t>
-  </si>
-  <si>
-    <t>윙입푸드</t>
-  </si>
-  <si>
     <t>아이텍</t>
   </si>
   <si>
@@ -711,9 +528,6 @@
     <t>비에이치</t>
   </si>
   <si>
-    <t>넥사다이내믹스</t>
-  </si>
-  <si>
     <t>한라IMS</t>
   </si>
   <si>
@@ -726,9 +540,6 @@
     <t>라온피플</t>
   </si>
   <si>
-    <t>씨씨에스</t>
-  </si>
-  <si>
     <t>감성코퍼레이션</t>
   </si>
   <si>
@@ -750,15 +561,6 @@
     <t>리메드</t>
   </si>
   <si>
-    <t>더라미</t>
-  </si>
-  <si>
-    <t>멤레이비티</t>
-  </si>
-  <si>
-    <t>대호에이엘</t>
-  </si>
-  <si>
     <t>고바이오랩</t>
   </si>
   <si>
@@ -771,18 +573,6 @@
     <t>에이비엘바이오</t>
   </si>
   <si>
-    <t>에코글로우</t>
-  </si>
-  <si>
-    <t>씨아이테크</t>
-  </si>
-  <si>
-    <t>이노진</t>
-  </si>
-  <si>
-    <t>다보링크</t>
-  </si>
-  <si>
     <t>녹십자웰빙</t>
   </si>
   <si>
@@ -795,18 +585,12 @@
     <t>싸이버원</t>
   </si>
   <si>
-    <t>시스웍</t>
-  </si>
-  <si>
     <t>SNT에너지</t>
   </si>
   <si>
     <t>GST</t>
   </si>
   <si>
-    <t>조이웍스앤코</t>
-  </si>
-  <si>
     <t>에이디테크놀로지</t>
   </si>
   <si>
@@ -831,9 +615,6 @@
     <t>PS일렉트로닉스</t>
   </si>
   <si>
-    <t>씨엔알리서치</t>
-  </si>
-  <si>
     <t>플래티어</t>
   </si>
   <si>
@@ -846,9 +627,6 @@
     <t>오스코텍</t>
   </si>
   <si>
-    <t>블리츠웨이엔터테인먼트</t>
-  </si>
-  <si>
     <t>일승</t>
   </si>
   <si>
@@ -858,24 +636,12 @@
     <t>박셀바이오</t>
   </si>
   <si>
-    <t>애드바이오텍</t>
-  </si>
-  <si>
     <t>HD현대에너지솔루션</t>
   </si>
   <si>
-    <t>에스아이리소스</t>
-  </si>
-  <si>
-    <t>수성웹툰</t>
-  </si>
-  <si>
     <t>두올</t>
   </si>
   <si>
-    <t>모아라이프플러스</t>
-  </si>
-  <si>
     <t>포커스에이아이</t>
   </si>
   <si>
@@ -897,16 +663,7 @@
     <t>아이패밀리에스씨</t>
   </si>
   <si>
-    <t>에스엘에스바이오</t>
-  </si>
-  <si>
-    <t>엣지파운드리</t>
-  </si>
-  <si>
     <t>엑스페릭스</t>
-  </si>
-  <si>
-    <t>프로이천</t>
   </si>
   <si>
     <t>탑머티리얼</t>
@@ -1284,15 +1041,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DE477B-1EB3-446F-9D10-A2F7378D6FCE}">
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>296</v>
+        <v>215</v>
       </c>
       <c r="B1" t="s">
-        <v>297</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1321,7 +1078,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>900250</v>
+        <v>222160</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -1329,7 +1086,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>222160</v>
+        <v>39290</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1337,7 +1094,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>8290</v>
+        <v>95190</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -1345,7 +1102,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>82660</v>
+        <v>41190</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -1353,7 +1110,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>89230</v>
+        <v>67370</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1361,7 +1118,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>39290</v>
+        <v>124500</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -1369,7 +1126,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>95190</v>
+        <v>23800</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -1377,7 +1134,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>84650</v>
+        <v>89790</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -1385,7 +1142,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>131100</v>
+        <v>199800</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1393,7 +1150,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>208640</v>
+        <v>67630</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1401,7 +1158,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>41190</v>
+        <v>176750</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1409,7 +1166,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>67370</v>
+        <v>277070</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1417,7 +1174,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>38530</v>
+        <v>128540</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1425,7 +1182,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>51780</v>
+        <v>53030</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -1433,7 +1190,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>124500</v>
+        <v>94480</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1441,7 +1198,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>23800</v>
+        <v>90360</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
@@ -1449,7 +1206,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>83790</v>
+        <v>25950</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
@@ -1457,7 +1214,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>89790</v>
+        <v>87600</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -1465,7 +1222,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>199800</v>
+        <v>317530</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
@@ -1473,7 +1230,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>304840</v>
+        <v>5870</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -1481,7 +1238,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>67630</v>
+        <v>37370</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -1489,7 +1246,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>176750</v>
+        <v>220180</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -1497,7 +1254,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>13720</v>
+        <v>95500</v>
       </c>
       <c r="B27" t="s">
         <v>25</v>
@@ -1505,7 +1262,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>277070</v>
+        <v>277880</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
@@ -1513,7 +1270,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>128540</v>
+        <v>221800</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
@@ -1521,7 +1278,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>20760</v>
+        <v>140670</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
@@ -1529,7 +1286,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>53030</v>
+        <v>5290</v>
       </c>
       <c r="B31" t="s">
         <v>29</v>
@@ -1537,7 +1294,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>154040</v>
+        <v>211050</v>
       </c>
       <c r="B32" t="s">
         <v>30</v>
@@ -1545,7 +1302,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>94480</v>
+        <v>226400</v>
       </c>
       <c r="B33" t="s">
         <v>31</v>
@@ -1553,7 +1310,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>90360</v>
+        <v>232680</v>
       </c>
       <c r="B34" t="s">
         <v>32</v>
@@ -1561,7 +1318,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>25950</v>
+        <v>240810</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -1569,7 +1326,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>23790</v>
+        <v>100660</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -1577,7 +1334,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>87600</v>
+        <v>82800</v>
       </c>
       <c r="B37" t="s">
         <v>35</v>
@@ -1585,7 +1342,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>317530</v>
+        <v>94970</v>
       </c>
       <c r="B38" t="s">
         <v>36</v>
@@ -1593,7 +1350,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>52420</v>
+        <v>118990</v>
       </c>
       <c r="B39" t="s">
         <v>37</v>
@@ -1601,7 +1358,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>66910</v>
+        <v>74610</v>
       </c>
       <c r="B40" t="s">
         <v>38</v>
@@ -1609,7 +1366,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>5870</v>
+        <v>36810</v>
       </c>
       <c r="B41" t="s">
         <v>39</v>
@@ -1617,7 +1374,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>37370</v>
+        <v>147830</v>
       </c>
       <c r="B42" t="s">
         <v>40</v>
@@ -1625,7 +1382,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>220180</v>
+        <v>10820</v>
       </c>
       <c r="B43" t="s">
         <v>41</v>
@@ -1633,7 +1390,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>95500</v>
+        <v>92870</v>
       </c>
       <c r="B44" t="s">
         <v>42</v>
@@ -1641,7 +1398,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>2680</v>
+        <v>222810</v>
       </c>
       <c r="B45" t="s">
         <v>43</v>
@@ -1649,7 +1406,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>277880</v>
+        <v>4985</v>
       </c>
       <c r="B46" t="s">
         <v>44</v>
@@ -1657,7 +1414,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>30350</v>
+        <v>85660</v>
       </c>
       <c r="B47" t="s">
         <v>45</v>
@@ -1665,7 +1422,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>221800</v>
+        <v>126880</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -1673,7 +1430,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>140670</v>
+        <v>229000</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
@@ -1681,7 +1438,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>5290</v>
+        <v>52020</v>
       </c>
       <c r="B50" t="s">
         <v>48</v>
@@ -1689,7 +1446,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>196490</v>
+        <v>156100</v>
       </c>
       <c r="B51" t="s">
         <v>49</v>
@@ -1697,7 +1454,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>211050</v>
+        <v>65450</v>
       </c>
       <c r="B52" t="s">
         <v>50</v>
@@ -1705,7 +1462,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>58110</v>
+        <v>24840</v>
       </c>
       <c r="B53" t="s">
         <v>51</v>
@@ -1713,7 +1470,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>226400</v>
+        <v>3010</v>
       </c>
       <c r="B54" t="s">
         <v>52</v>
@@ -1721,7 +1478,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>232680</v>
+        <v>1250</v>
       </c>
       <c r="B55" t="s">
         <v>53</v>
@@ -1729,7 +1486,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>240810</v>
+        <v>6570</v>
       </c>
       <c r="B56" t="s">
         <v>54</v>
@@ -1737,7 +1494,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>100660</v>
+        <v>217620</v>
       </c>
       <c r="B57" t="s">
         <v>55</v>
@@ -1745,7 +1502,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>82800</v>
+        <v>305090</v>
       </c>
       <c r="B58" t="s">
         <v>56</v>
@@ -1753,7 +1510,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>94970</v>
+        <v>64240</v>
       </c>
       <c r="B59" t="s">
         <v>57</v>
@@ -1761,7 +1518,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>118990</v>
+        <v>250</v>
       </c>
       <c r="B60" t="s">
         <v>58</v>
@@ -1769,7 +1526,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>9810</v>
+        <v>224110</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
@@ -1777,7 +1534,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>74610</v>
+        <v>75970</v>
       </c>
       <c r="B62" t="s">
         <v>60</v>
@@ -1785,7 +1542,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>204840</v>
+        <v>78600</v>
       </c>
       <c r="B63" t="s">
         <v>61</v>
@@ -1793,7 +1550,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>227950</v>
+        <v>93640</v>
       </c>
       <c r="B64" t="s">
         <v>62</v>
@@ -1801,7 +1558,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>36810</v>
+        <v>105330</v>
       </c>
       <c r="B65" t="s">
         <v>63</v>
@@ -1809,7 +1566,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>23960</v>
+        <v>94360</v>
       </c>
       <c r="B66" t="s">
         <v>64</v>
@@ -1817,7 +1574,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>147830</v>
+        <v>81150</v>
       </c>
       <c r="B67" t="s">
         <v>65</v>
@@ -1825,7 +1582,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>5110</v>
+        <v>39740</v>
       </c>
       <c r="B68" t="s">
         <v>66</v>
@@ -1833,7 +1590,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>49080</v>
+        <v>42940</v>
       </c>
       <c r="B69" t="s">
         <v>67</v>
@@ -1841,7 +1598,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>313760</v>
+        <v>84695</v>
       </c>
       <c r="B70" t="s">
         <v>68</v>
@@ -1849,7 +1606,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>10820</v>
+        <v>101360</v>
       </c>
       <c r="B71" t="s">
         <v>69</v>
@@ -1857,7 +1614,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>92870</v>
+        <v>82270</v>
       </c>
       <c r="B72" t="s">
         <v>70</v>
@@ -1865,7 +1622,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>222810</v>
+        <v>250060</v>
       </c>
       <c r="B73" t="s">
         <v>71</v>
@@ -1873,7 +1630,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>4985</v>
+        <v>83500</v>
       </c>
       <c r="B74" t="s">
         <v>72</v>
@@ -1881,7 +1638,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>85660</v>
+        <v>141080</v>
       </c>
       <c r="B75" t="s">
         <v>73</v>
@@ -1889,7 +1646,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>32980</v>
+        <v>46120</v>
       </c>
       <c r="B76" t="s">
         <v>74</v>
@@ -1897,7 +1654,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>84680</v>
+        <v>178320</v>
       </c>
       <c r="B77" t="s">
         <v>75</v>
@@ -1905,7 +1662,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>258610</v>
+        <v>59090</v>
       </c>
       <c r="B78" t="s">
         <v>76</v>
@@ -1913,7 +1670,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>126880</v>
+        <v>138610</v>
       </c>
       <c r="B79" t="s">
         <v>77</v>
@@ -1921,7 +1678,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>229000</v>
+        <v>246710</v>
       </c>
       <c r="B80" t="s">
         <v>78</v>
@@ -1929,7 +1686,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>52020</v>
+        <v>9420</v>
       </c>
       <c r="B81" t="s">
         <v>79</v>
@@ -1937,7 +1694,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>156100</v>
+        <v>234300</v>
       </c>
       <c r="B82" t="s">
         <v>80</v>
@@ -1945,7 +1702,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>65450</v>
+        <v>7660</v>
       </c>
       <c r="B83" t="s">
         <v>81</v>
@@ -1953,7 +1710,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>19570</v>
+        <v>242040</v>
       </c>
       <c r="B84" t="s">
         <v>82</v>
@@ -1961,7 +1718,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>24840</v>
+        <v>39030</v>
       </c>
       <c r="B85" t="s">
         <v>83</v>
@@ -1969,7 +1726,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>3010</v>
+        <v>86520</v>
       </c>
       <c r="B86" t="s">
         <v>84</v>
@@ -1977,7 +1734,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>1250</v>
+        <v>214680</v>
       </c>
       <c r="B87" t="s">
         <v>85</v>
@@ -1985,7 +1742,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>6570</v>
+        <v>14190</v>
       </c>
       <c r="B88" t="s">
         <v>86</v>
@@ -1993,7 +1750,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>217620</v>
+        <v>89140</v>
       </c>
       <c r="B89" t="s">
         <v>87</v>
@@ -2001,7 +1758,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>270520</v>
+        <v>203400</v>
       </c>
       <c r="B90" t="s">
         <v>88</v>
@@ -2009,7 +1766,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>305090</v>
+        <v>47560</v>
       </c>
       <c r="B91" t="s">
         <v>89</v>
@@ -2017,7 +1774,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>64240</v>
+        <v>48410</v>
       </c>
       <c r="B92" t="s">
         <v>90</v>
@@ -2025,7 +1782,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>79970</v>
+        <v>41910</v>
       </c>
       <c r="B93" t="s">
         <v>91</v>
@@ -2033,7 +1790,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="B94" t="s">
         <v>92</v>
@@ -2041,7 +1798,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>224110</v>
+        <v>267320</v>
       </c>
       <c r="B95" t="s">
         <v>93</v>
@@ -2049,7 +1806,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>60230</v>
+        <v>60370</v>
       </c>
       <c r="B96" t="s">
         <v>94</v>
@@ -2057,7 +1814,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>75970</v>
+        <v>220100</v>
       </c>
       <c r="B97" t="s">
         <v>95</v>
@@ -2065,7 +1822,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>78600</v>
+        <v>44990</v>
       </c>
       <c r="B98" t="s">
         <v>96</v>
@@ -2073,7 +1830,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>93640</v>
+        <v>190510</v>
       </c>
       <c r="B99" t="s">
         <v>97</v>
@@ -2081,7 +1838,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>105330</v>
+        <v>58970</v>
       </c>
       <c r="B100" t="s">
         <v>98</v>
@@ -2089,7 +1846,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>44380</v>
+        <v>259630</v>
       </c>
       <c r="B101" t="s">
         <v>99</v>
@@ -2097,7 +1854,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>94360</v>
+        <v>147760</v>
       </c>
       <c r="B102" t="s">
         <v>100</v>
@@ -2105,7 +1862,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>81150</v>
+        <v>25320</v>
       </c>
       <c r="B103" t="s">
         <v>101</v>
@@ -2113,7 +1870,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>39740</v>
+        <v>24060</v>
       </c>
       <c r="B104" t="s">
         <v>102</v>
@@ -2121,7 +1878,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>42940</v>
+        <v>174900</v>
       </c>
       <c r="B105" t="s">
         <v>103</v>
@@ -2129,7 +1886,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>84695</v>
+        <v>101490</v>
       </c>
       <c r="B106" t="s">
         <v>104</v>
@@ -2137,7 +1894,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>101360</v>
+        <v>300080</v>
       </c>
       <c r="B107" t="s">
         <v>105</v>
@@ -2145,7 +1902,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>82270</v>
+        <v>232140</v>
       </c>
       <c r="B108" t="s">
         <v>106</v>
@@ -2153,7 +1910,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>250060</v>
+        <v>82920</v>
       </c>
       <c r="B109" t="s">
         <v>107</v>
@@ -2161,7 +1918,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>83500</v>
+        <v>42510</v>
       </c>
       <c r="B110" t="s">
         <v>108</v>
@@ -2169,7 +1926,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>141080</v>
+        <v>84370</v>
       </c>
       <c r="B111" t="s">
         <v>109</v>
@@ -2177,7 +1934,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>185490</v>
+        <v>149980</v>
       </c>
       <c r="B112" t="s">
         <v>110</v>
@@ -2185,7 +1942,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>46120</v>
+        <v>40300</v>
       </c>
       <c r="B113" t="s">
         <v>111</v>
@@ -2193,7 +1950,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>178320</v>
+        <v>5690</v>
       </c>
       <c r="B114" t="s">
         <v>112</v>
@@ -2201,7 +1958,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>59090</v>
+        <v>7680</v>
       </c>
       <c r="B115" t="s">
         <v>113</v>
@@ -2209,7 +1966,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>138610</v>
+        <v>246960</v>
       </c>
       <c r="B116" t="s">
         <v>114</v>
@@ -2217,7 +1974,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>54300</v>
+        <v>187420</v>
       </c>
       <c r="B117" t="s">
         <v>115</v>
@@ -2225,7 +1982,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>32280</v>
+        <v>80470</v>
       </c>
       <c r="B118" t="s">
         <v>116</v>
@@ -2233,7 +1990,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>246710</v>
+        <v>96870</v>
       </c>
       <c r="B119" t="s">
         <v>117</v>
@@ -2241,7 +1998,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>9420</v>
+        <v>99190</v>
       </c>
       <c r="B120" t="s">
         <v>118</v>
@@ -2249,7 +2006,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>73570</v>
+        <v>179900</v>
       </c>
       <c r="B121" t="s">
         <v>119</v>
@@ -2257,7 +2014,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>234300</v>
+        <v>134060</v>
       </c>
       <c r="B122" t="s">
         <v>120</v>
@@ -2265,7 +2022,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>7660</v>
+        <v>378850</v>
       </c>
       <c r="B123" t="s">
         <v>121</v>
@@ -2273,7 +2030,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>242040</v>
+        <v>33100</v>
       </c>
       <c r="B124" t="s">
         <v>122</v>
@@ -2281,7 +2038,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>73640</v>
+        <v>2420</v>
       </c>
       <c r="B125" t="s">
         <v>123</v>
@@ -2289,7 +2046,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>39030</v>
+        <v>42370</v>
       </c>
       <c r="B126" t="s">
         <v>124</v>
@@ -2297,7 +2054,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>86520</v>
+        <v>42700</v>
       </c>
       <c r="B127" t="s">
         <v>125</v>
@@ -2305,7 +2062,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>214680</v>
+        <v>110990</v>
       </c>
       <c r="B128" t="s">
         <v>126</v>
@@ -2313,7 +2070,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>101400</v>
+        <v>25870</v>
       </c>
       <c r="B129" t="s">
         <v>127</v>
@@ -2321,7 +2078,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>14190</v>
+        <v>214150</v>
       </c>
       <c r="B130" t="s">
         <v>128</v>
@@ -2329,7 +2086,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>89140</v>
+        <v>128820</v>
       </c>
       <c r="B131" t="s">
         <v>129</v>
@@ -2337,7 +2094,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>203400</v>
+        <v>322510</v>
       </c>
       <c r="B132" t="s">
         <v>130</v>
@@ -2345,7 +2102,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>47560</v>
+        <v>121850</v>
       </c>
       <c r="B133" t="s">
         <v>131</v>
@@ -2353,7 +2110,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>48410</v>
+        <v>25820</v>
       </c>
       <c r="B134" t="s">
         <v>132</v>
@@ -2361,7 +2118,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>205470</v>
+        <v>196170</v>
       </c>
       <c r="B135" t="s">
         <v>133</v>
@@ -2369,7 +2126,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>41910</v>
+        <v>225</v>
       </c>
       <c r="B136" t="s">
         <v>134</v>
@@ -2377,7 +2134,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>440</v>
+        <v>117670</v>
       </c>
       <c r="B137" t="s">
         <v>135</v>
@@ -2385,7 +2142,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>219750</v>
+        <v>112040</v>
       </c>
       <c r="B138" t="s">
         <v>136</v>
@@ -2393,7 +2150,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>267320</v>
+        <v>87010</v>
       </c>
       <c r="B139" t="s">
         <v>137</v>
@@ -2401,7 +2158,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>60370</v>
+        <v>290090</v>
       </c>
       <c r="B140" t="s">
         <v>138</v>
@@ -2409,7 +2166,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>88290</v>
+        <v>54930</v>
       </c>
       <c r="B141" t="s">
         <v>139</v>
@@ -2417,7 +2174,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>220100</v>
+        <v>79170</v>
       </c>
       <c r="B142" t="s">
         <v>140</v>
@@ -2425,7 +2182,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>44990</v>
+        <v>33500</v>
       </c>
       <c r="B143" t="s">
         <v>141</v>
@@ -2433,7 +2190,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>190510</v>
+        <v>115570</v>
       </c>
       <c r="B144" t="s">
         <v>142</v>
@@ -2441,7 +2198,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>58970</v>
+        <v>189330</v>
       </c>
       <c r="B145" t="s">
         <v>143</v>
@@ -2449,7 +2206,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>227100</v>
+        <v>66970</v>
       </c>
       <c r="B146" t="s">
         <v>144</v>
@@ -2457,7 +2214,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>259630</v>
+        <v>293780</v>
       </c>
       <c r="B147" t="s">
         <v>145</v>
@@ -2465,7 +2222,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>147760</v>
+        <v>317850</v>
       </c>
       <c r="B148" t="s">
         <v>146</v>
@@ -2473,7 +2230,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>25320</v>
+        <v>125210</v>
       </c>
       <c r="B149" t="s">
         <v>147</v>
@@ -2481,7 +2238,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>24060</v>
+        <v>4835</v>
       </c>
       <c r="B150" t="s">
         <v>148</v>
@@ -2489,7 +2246,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>210120</v>
+        <v>279600</v>
       </c>
       <c r="B151" t="s">
         <v>149</v>
@@ -2497,7 +2254,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>174900</v>
+        <v>157</v>
       </c>
       <c r="B152" t="s">
         <v>150</v>
@@ -2505,7 +2262,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>101490</v>
+        <v>520</v>
       </c>
       <c r="B153" t="s">
         <v>151</v>
@@ -2513,7 +2270,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>300080</v>
+        <v>73010</v>
       </c>
       <c r="B154" t="s">
         <v>152</v>
@@ -2521,31 +2278,31 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>13700</v>
+        <v>263920</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>232140</v>
+        <v>82740</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>82920</v>
+        <v>127120</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>42510</v>
+        <v>52690</v>
       </c>
       <c r="B158" t="s">
         <v>156</v>
@@ -2553,7 +2310,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>84370</v>
+        <v>85670</v>
       </c>
       <c r="B159" t="s">
         <v>157</v>
@@ -2561,7 +2318,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>149980</v>
+        <v>281740</v>
       </c>
       <c r="B160" t="s">
         <v>158</v>
@@ -2569,7 +2326,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>40300</v>
+        <v>323350</v>
       </c>
       <c r="B161" t="s">
         <v>159</v>
@@ -2577,7 +2334,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>5690</v>
+        <v>1527</v>
       </c>
       <c r="B162" t="s">
         <v>160</v>
@@ -2585,7 +2342,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>7680</v>
+        <v>119830</v>
       </c>
       <c r="B163" t="s">
         <v>161</v>
@@ -2593,23 +2350,23 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>246960</v>
+        <v>178780</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>187420</v>
+        <v>272110</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>80470</v>
+        <v>115180</v>
       </c>
       <c r="B166" t="s">
         <v>164</v>
@@ -2617,7 +2374,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>96870</v>
+        <v>264850</v>
       </c>
       <c r="B167" t="s">
         <v>165</v>
@@ -2625,7 +2382,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>99190</v>
+        <v>90460</v>
       </c>
       <c r="B168" t="s">
         <v>166</v>
@@ -2633,7 +2390,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>179900</v>
+        <v>92460</v>
       </c>
       <c r="B169" t="s">
         <v>167</v>
@@ -2641,7 +2398,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>134060</v>
+        <v>103230</v>
       </c>
       <c r="B170" t="s">
         <v>168</v>
@@ -2649,7 +2406,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>378850</v>
+        <v>319660</v>
       </c>
       <c r="B171" t="s">
         <v>169</v>
@@ -2657,7 +2414,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>33100</v>
+        <v>300120</v>
       </c>
       <c r="B172" t="s">
         <v>170</v>
@@ -2665,7 +2422,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>33540</v>
+        <v>36620</v>
       </c>
       <c r="B173" t="s">
         <v>171</v>
@@ -2673,7 +2430,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>2420</v>
+        <v>161580</v>
       </c>
       <c r="B174" t="s">
         <v>172</v>
@@ -2681,7 +2438,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>42370</v>
+        <v>11690</v>
       </c>
       <c r="B175" t="s">
         <v>173</v>
@@ -2689,7 +2446,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>42700</v>
+        <v>182400</v>
       </c>
       <c r="B176" t="s">
         <v>174</v>
@@ -2697,7 +2454,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>110990</v>
+        <v>96610</v>
       </c>
       <c r="B177" t="s">
         <v>175</v>
@@ -2705,7 +2462,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>98660</v>
+        <v>131290</v>
       </c>
       <c r="B178" t="s">
         <v>176</v>
@@ -2713,7 +2470,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>25870</v>
+        <v>302550</v>
       </c>
       <c r="B179" t="s">
         <v>177</v>
@@ -2721,7 +2478,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>214150</v>
+        <v>348150</v>
       </c>
       <c r="B180" t="s">
         <v>178</v>
@@ -2729,7 +2486,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>128820</v>
+        <v>200350</v>
       </c>
       <c r="B181" t="s">
         <v>179</v>
@@ -2737,7 +2494,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>322510</v>
+        <v>307180</v>
       </c>
       <c r="B182" t="s">
         <v>180</v>
@@ -2745,7 +2502,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>121850</v>
+        <v>298380</v>
       </c>
       <c r="B183" t="s">
         <v>181</v>
@@ -2753,7 +2510,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>25820</v>
+        <v>234690</v>
       </c>
       <c r="B184" t="s">
         <v>182</v>
@@ -2761,7 +2518,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>196170</v>
+        <v>320000</v>
       </c>
       <c r="B185" t="s">
         <v>183</v>
@@ -2769,7 +2526,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>225</v>
+        <v>215090</v>
       </c>
       <c r="B186" t="s">
         <v>184</v>
@@ -2777,7 +2534,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>117670</v>
+        <v>356890</v>
       </c>
       <c r="B187" t="s">
         <v>185</v>
@@ -2785,7 +2542,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>79190</v>
+        <v>100840</v>
       </c>
       <c r="B188" t="s">
         <v>186</v>
@@ -2793,7 +2550,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>112040</v>
+        <v>83450</v>
       </c>
       <c r="B189" t="s">
         <v>187</v>
@@ -2801,7 +2558,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>87010</v>
+        <v>200710</v>
       </c>
       <c r="B190" t="s">
         <v>188</v>
@@ -2809,7 +2566,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>290090</v>
+        <v>153460</v>
       </c>
       <c r="B191" t="s">
         <v>189</v>
@@ -2817,7 +2574,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>54930</v>
+        <v>67310</v>
       </c>
       <c r="B192" t="s">
         <v>190</v>
@@ -2825,7 +2582,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>79170</v>
+        <v>45340</v>
       </c>
       <c r="B193" t="s">
         <v>191</v>
@@ -2833,7 +2590,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>258790</v>
+        <v>353200</v>
       </c>
       <c r="B194" t="s">
         <v>192</v>
@@ -2841,7 +2598,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>33500</v>
+        <v>347700</v>
       </c>
       <c r="B195" t="s">
         <v>193</v>
@@ -2849,7 +2606,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>115570</v>
+        <v>91440</v>
       </c>
       <c r="B196" t="s">
         <v>194</v>
@@ -2857,7 +2614,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>57680</v>
+        <v>332570</v>
       </c>
       <c r="B197" t="s">
         <v>195</v>
@@ -2865,7 +2622,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>189330</v>
+        <v>367000</v>
       </c>
       <c r="B198" t="s">
         <v>196</v>
@@ -2873,7 +2630,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>66970</v>
+        <v>204630</v>
       </c>
       <c r="B199" t="s">
         <v>197</v>
@@ -2881,7 +2638,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>293780</v>
+        <v>3720</v>
       </c>
       <c r="B200" t="s">
         <v>198</v>
@@ -2889,7 +2646,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>115530</v>
+        <v>39200</v>
       </c>
       <c r="B201" t="s">
         <v>199</v>
@@ -2897,7 +2654,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>317850</v>
+        <v>333430</v>
       </c>
       <c r="B202" t="s">
         <v>200</v>
@@ -2905,7 +2662,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>125210</v>
+        <v>187660</v>
       </c>
       <c r="B203" t="s">
         <v>201</v>
@@ -2913,7 +2670,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>12170</v>
+        <v>323990</v>
       </c>
       <c r="B204" t="s">
         <v>202</v>
@@ -2921,7 +2678,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>4835</v>
+        <v>322000</v>
       </c>
       <c r="B205" t="s">
         <v>203</v>
@@ -2929,7 +2686,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>68940</v>
+        <v>16740</v>
       </c>
       <c r="B206" t="s">
         <v>204</v>
@@ -2937,23 +2694,23 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>279600</v>
+        <v>105</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>157</v>
+        <v>331380</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>46970</v>
+        <v>11500</v>
       </c>
       <c r="B209" t="s">
         <v>207</v>
@@ -2961,7 +2718,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>278650</v>
+        <v>8110</v>
       </c>
       <c r="B210" t="s">
         <v>208</v>
@@ -2969,23 +2726,23 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>520</v>
+        <v>334970</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>73010</v>
+        <v>327260</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>82740</v>
+        <v>114840</v>
       </c>
       <c r="B213" t="s">
         <v>211</v>
@@ -2993,7 +2750,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>127120</v>
+        <v>317770</v>
       </c>
       <c r="B214" t="s">
         <v>212</v>
@@ -3001,7 +2758,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>263920</v>
+        <v>360070</v>
       </c>
       <c r="B215" t="s">
         <v>213</v>
@@ -3009,658 +2766,10 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>52690</v>
+        <v>460930</v>
       </c>
       <c r="B216" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217">
-        <v>85670</v>
-      </c>
-      <c r="B217" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A218">
-        <v>281740</v>
-      </c>
-      <c r="B218" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A219">
-        <v>323350</v>
-      </c>
-      <c r="B219" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A220">
-        <v>1527</v>
-      </c>
-      <c r="B220" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A221">
-        <v>94860</v>
-      </c>
-      <c r="B221" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A222">
-        <v>284620</v>
-      </c>
-      <c r="B222" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A223">
-        <v>900340</v>
-      </c>
-      <c r="B223" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A224">
-        <v>119830</v>
-      </c>
-      <c r="B224" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225">
-        <v>272110</v>
-      </c>
-      <c r="B225" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226">
-        <v>178780</v>
-      </c>
-      <c r="B226" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227">
-        <v>115180</v>
-      </c>
-      <c r="B227" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A228">
-        <v>264850</v>
-      </c>
-      <c r="B228" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229">
-        <v>90460</v>
-      </c>
-      <c r="B229" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230">
-        <v>351320</v>
-      </c>
-      <c r="B230" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231">
-        <v>92460</v>
-      </c>
-      <c r="B231" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232">
-        <v>103230</v>
-      </c>
-      <c r="B232" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A233">
-        <v>319660</v>
-      </c>
-      <c r="B233" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234">
-        <v>300120</v>
-      </c>
-      <c r="B234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A235">
-        <v>66790</v>
-      </c>
-      <c r="B235" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236">
-        <v>36620</v>
-      </c>
-      <c r="B236" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A237">
-        <v>161580</v>
-      </c>
-      <c r="B237" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A238">
-        <v>11690</v>
-      </c>
-      <c r="B238" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A239">
-        <v>182400</v>
-      </c>
-      <c r="B239" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240">
-        <v>96610</v>
-      </c>
-      <c r="B240" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A241">
-        <v>131290</v>
-      </c>
-      <c r="B241" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A242">
-        <v>302550</v>
-      </c>
-      <c r="B242" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A243">
-        <v>32860</v>
-      </c>
-      <c r="B243" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A244">
-        <v>72770</v>
-      </c>
-      <c r="B244" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A245">
-        <v>69460</v>
-      </c>
-      <c r="B245" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A246">
-        <v>348150</v>
-      </c>
-      <c r="B246" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A247">
-        <v>200350</v>
-      </c>
-      <c r="B247" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A248">
-        <v>307180</v>
-      </c>
-      <c r="B248" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A249">
-        <v>298380</v>
-      </c>
-      <c r="B249" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250">
-        <v>159910</v>
-      </c>
-      <c r="B250" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251">
-        <v>4920</v>
-      </c>
-      <c r="B251" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A252">
-        <v>344860</v>
-      </c>
-      <c r="B252" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A253">
-        <v>340360</v>
-      </c>
-      <c r="B253" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254">
-        <v>234690</v>
-      </c>
-      <c r="B254" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A255">
-        <v>320000</v>
-      </c>
-      <c r="B255" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256">
-        <v>215090</v>
-      </c>
-      <c r="B256" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257">
-        <v>356890</v>
-      </c>
-      <c r="B257" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A258">
-        <v>269620</v>
-      </c>
-      <c r="B258" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259">
-        <v>100840</v>
-      </c>
-      <c r="B259" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260">
-        <v>83450</v>
-      </c>
-      <c r="B260" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A261">
-        <v>309930</v>
-      </c>
-      <c r="B261" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A262">
-        <v>200710</v>
-      </c>
-      <c r="B262" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263">
-        <v>153460</v>
-      </c>
-      <c r="B263" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A264">
-        <v>67310</v>
-      </c>
-      <c r="B264" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A265">
-        <v>45340</v>
-      </c>
-      <c r="B265" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266">
-        <v>353200</v>
-      </c>
-      <c r="B266" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A267">
-        <v>347700</v>
-      </c>
-      <c r="B267" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A268">
-        <v>91440</v>
-      </c>
-      <c r="B268" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A269">
-        <v>332570</v>
-      </c>
-      <c r="B269" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A270">
-        <v>359090</v>
-      </c>
-      <c r="B270" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A271">
-        <v>367000</v>
-      </c>
-      <c r="B271" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272">
-        <v>204630</v>
-      </c>
-      <c r="B272" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273">
-        <v>3720</v>
-      </c>
-      <c r="B273" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274">
-        <v>39200</v>
-      </c>
-      <c r="B274" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275">
-        <v>369370</v>
-      </c>
-      <c r="B275" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276">
-        <v>333430</v>
-      </c>
-      <c r="B276" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277">
-        <v>187660</v>
-      </c>
-      <c r="B277" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278">
-        <v>323990</v>
-      </c>
-      <c r="B278" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279">
-        <v>179530</v>
-      </c>
-      <c r="B279" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280">
-        <v>322000</v>
-      </c>
-      <c r="B280" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281">
-        <v>65420</v>
-      </c>
-      <c r="B281" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282">
-        <v>84180</v>
-      </c>
-      <c r="B282" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283">
-        <v>16740</v>
-      </c>
-      <c r="B283" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284">
-        <v>142760</v>
-      </c>
-      <c r="B284" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285">
-        <v>331380</v>
-      </c>
-      <c r="B285" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286">
-        <v>105</v>
-      </c>
-      <c r="B286" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287">
-        <v>11500</v>
-      </c>
-      <c r="B287" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288">
-        <v>8110</v>
-      </c>
-      <c r="B288" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289">
-        <v>327260</v>
-      </c>
-      <c r="B289" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290">
-        <v>334970</v>
-      </c>
-      <c r="B290" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291">
-        <v>114840</v>
-      </c>
-      <c r="B291" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292">
-        <v>246250</v>
-      </c>
-      <c r="B292" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293">
-        <v>105550</v>
-      </c>
-      <c r="B293" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294">
-        <v>317770</v>
-      </c>
-      <c r="B294" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295">
-        <v>321260</v>
-      </c>
-      <c r="B295" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296">
-        <v>360070</v>
-      </c>
-      <c r="B296" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297">
-        <v>460930</v>
-      </c>
-      <c r="B297" t="s">
-        <v>295</v>
       </c>
     </row>
   </sheetData>
